--- a/public/excel_upload/assets/UPLOAD_tbluser.xlsx
+++ b/public/excel_upload/assets/UPLOAD_tbluser.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="240" yWindow="60" windowWidth="8595" windowHeight="7230"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>user_name</t>
   </si>
@@ -75,31 +76,54 @@
   </si>
   <si>
     <t>last_login</t>
+  </si>
+  <si>
+    <t>qualification</t>
+  </si>
+  <si>
+    <t>pan_no</t>
+  </si>
+  <si>
+    <t>aadhar_no</t>
+  </si>
+  <si>
+    <t>joined_date</t>
+  </si>
+  <si>
+    <t>department_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -107,31 +131,38 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,36 +452,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.711426" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="10.568848" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="13.996582" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12.854004" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="13.996582" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.711426" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="6.998291" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="8.140869" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="8.140869" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="11.711426" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="9.283447000000001" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="5.855713" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="6.998291" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="9.283447000000001" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="18.709717" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="11.711426" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="6.998291" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="17.567139" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="8.140869" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="12.854004" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,19 +522,42 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/excel_upload/assets/UPLOAD_tbluser.xlsx
+++ b/public/excel_upload/assets/UPLOAD_tbluser.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\unused\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="8595" windowHeight="7230"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11595"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>user_name</t>
   </si>
@@ -78,19 +83,16 @@
     <t>last_login</t>
   </si>
   <si>
-    <t>qualification</t>
-  </si>
-  <si>
-    <t>pan_no</t>
-  </si>
-  <si>
-    <t>aadhar_no</t>
-  </si>
-  <si>
     <t>joined_date</t>
   </si>
   <si>
-    <t>department_id</t>
+    <t>employee_no</t>
+  </si>
+  <si>
+    <t>pan_card</t>
+  </si>
+  <si>
+    <t>aadhar_card</t>
   </si>
 </sst>
 </file>
@@ -162,6 +164,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -209,7 +214,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -244,7 +249,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -453,15 +458,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,19 +547,16 @@
         <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
